--- a/data/trans_dic/P05B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P05B_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,27</t>
+          <t>2,2; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,37</t>
+          <t>0,79; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,25</t>
+          <t>0,71; 2,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,84</t>
+          <t>1,2; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,61</t>
+          <t>4,04; 6,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,18</t>
+          <t>0,79; 2,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,85</t>
+          <t>1,69; 3,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,7</t>
+          <t>1,04; 2,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,07</t>
+          <t>3,51; 5,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,94</t>
+          <t>0,91; 1,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,87</t>
+          <t>1,45; 2,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,78</t>
+          <t>1,27; 2,5</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,78</t>
+          <t>2,07; 3,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,33</t>
+          <t>1,08; 2,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,08</t>
+          <t>0,96; 2,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,02</t>
+          <t>0,32; 1,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,55</t>
+          <t>3,49; 5,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,83</t>
+          <t>1,43; 2,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,84</t>
+          <t>1,49; 2,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,38</t>
+          <t>0,69; 1,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,22</t>
+          <t>2,96; 4,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,34</t>
+          <t>1,39; 2,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,23</t>
+          <t>1,34; 2,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,08</t>
+          <t>0,59; 1,1</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,9</t>
+          <t>1,73; 4,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,17</t>
+          <t>1,15; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,19</t>
+          <t>0,51; 3,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,31</t>
+          <t>0,95; 3,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,96</t>
+          <t>2,78; 6,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,2</t>
+          <t>0,4; 2,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,84</t>
+          <t>0,76; 3,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,88</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,04</t>
+          <t>2,5; 4,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,71</t>
+          <t>0,96; 2,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,35</t>
+          <t>0,81; 2,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,64</t>
+          <t>1,17; 2,61</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,61</t>
+          <t>2,42; 3,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,2</t>
+          <t>1,22; 2,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,78</t>
+          <t>1,0; 1,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,55</t>
+          <t>0,79; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,43</t>
+          <t>4,0; 5,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,12</t>
+          <t>1,27; 2,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,69</t>
+          <t>1,72; 2,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,63</t>
+          <t>1,0; 1,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 4,35</t>
+          <t>3,38; 4,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,98</t>
+          <t>1,33; 1,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,14</t>
+          <t>1,47; 2,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,47</t>
+          <t>0,96; 1,48</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12987</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>25212</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>22231; 44016</t>
+          <t>22647; 44694</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7837; 22957</t>
+          <t>7716; 22497</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4953; 16904</t>
+          <t>5361; 17367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6736; 19693</t>
+          <t>6887; 19744</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53877; 86953</t>
+          <t>53148; 83826</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9818; 28964</t>
+          <t>10423; 27447</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16374; 37969</t>
+          <t>16702; 38063</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8380; 20295</t>
+          <t>8477; 20254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81346; 118863</t>
+          <t>82420; 122392</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22076; 44481</t>
+          <t>21008; 45086</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24950; 50013</t>
+          <t>25172; 49461</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17447; 35161</t>
+          <t>17735; 34861</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20975</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34387</t>
+          <t>35239</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>36193; 64058</t>
+          <t>34978; 64960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20560; 45549</t>
+          <t>21168; 44562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20325; 43151</t>
+          <t>19965; 42019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6032; 23429</t>
+          <t>7060; 24036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55932; 87993</t>
+          <t>55387; 87536</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24646; 49541</t>
+          <t>25124; 49155</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29788; 56211</t>
+          <t>29617; 54477</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13435; 30936</t>
+          <t>15059; 32306</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97230; 138257</t>
+          <t>96933; 143106</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50826; 86817</t>
+          <t>51399; 86347</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55243; 90287</t>
+          <t>54215; 89478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24060; 48894</t>
+          <t>25921; 48413</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12211</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>25021</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9866; 26915</t>
+          <t>9491; 26464</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5208; 19928</t>
+          <t>5520; 20584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2744; 17398</t>
+          <t>2796; 16365</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6042; 21373</t>
+          <t>6728; 23914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13433; 33180</t>
+          <t>13263; 31360</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1805; 10055</t>
+          <t>1819; 10731</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4180; 15589</t>
+          <t>4197; 16555</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6160; 18923</t>
+          <t>6920; 20403</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25954; 51637</t>
+          <t>25593; 51202</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9084; 25318</t>
+          <t>8977; 25890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8202; 25745</t>
+          <t>8817; 26293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15406; 34383</t>
+          <t>16919; 37601</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45413</t>
+          <t>47605</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82578</t>
+          <t>85473</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>77821; 118038</t>
+          <t>79226; 119159</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42844; 75039</t>
+          <t>41610; 74446</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32505; 60126</t>
+          <t>33725; 61192</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24713; 53409</t>
+          <t>27609; 53603</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>135783; 183332</t>
+          <t>135032; 183299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42182; 75022</t>
+          <t>44778; 74893</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60196; 94702</t>
+          <t>60414; 96336</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33494; 59525</t>
+          <t>37231; 62951</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224001; 289091</t>
+          <t>225037; 289010</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94252; 137763</t>
+          <t>92509; 136359</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102616; 147386</t>
+          <t>101032; 145953</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>65943; 103982</t>
+          <t>69374; 107159</t>
         </is>
       </c>
     </row>
